--- a/CustomerA-Date-Version-LM-EPL.xlsx
+++ b/CustomerA-Date-Version-LM-EPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yadmitrieva/EPL Tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4729DE1E-C425-154C-9FD5-8431F00F4ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38349B24-04CF-734F-85A4-D6DA725A2F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{DDE073C0-B8B2-4473-B43C-E765446080E4}"/>
   </bookViews>
@@ -608,11 +608,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1179,24 +1179,24 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
@@ -5289,8 +5289,7 @@
       <c r="F436" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
+  <mergeCells count="1">
     <mergeCell ref="A9:F9"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -5301,12 +5300,36 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Remark xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96" xsi:nil="true"/>
+    <PRODUCT__x002f__RANGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Value>-</Value>
+    </PRODUCT__x002f__RANGE>
+    <DOC_DESCRIPTION xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DOC_TYPE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <IDENTIFICATION_REFERENCE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TAG_1 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TAG_2 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <REF_YEAR__x002f__ANNEE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">2023</REF_YEAR__x002f__ANNEE>
+    <PERIOD xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DOC_LANGUAGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Value>French (France)</Value>
+    </DOC_LANGUAGE>
+    <DOMAIN xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MARKET__x002f__MARCHE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <DEPT_AUTOR xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TARGET_AUDIENCE__x002f__DESTINATAIRE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <DOC_STATUS xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">Update Version/Version Actuelle</DOC_STATUS>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8994,42 +9017,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Remark xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96" xsi:nil="true"/>
-    <PRODUCT__x002f__RANGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Value>-</Value>
-    </PRODUCT__x002f__RANGE>
-    <DOC_DESCRIPTION xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DOC_TYPE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <IDENTIFICATION_REFERENCE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TAG_1 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TAG_2 xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <REF_YEAR__x002f__ANNEE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">2023</REF_YEAR__x002f__ANNEE>
-    <PERIOD xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DOC_LANGUAGE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Value>French (France)</Value>
-    </DOC_LANGUAGE>
-    <DOMAIN xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e83e573-fb93-452c-9f3b-7b87af48cc96">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MARKET__x002f__MARCHE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <DEPT_AUTOR xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TARGET_AUDIENCE__x002f__DESTINATAIRE xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <DOC_STATUS xmlns="dc163805-5a8a-4bac-b0c0-60a9bfcd087a">Update Version/Version Actuelle</DOC_STATUS>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB17129-D171-45DC-AA3C-DECEAA032B19}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BAE7EAD-CAED-4699-A6FD-BC11EEB22633}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e83e573-fb93-452c-9f3b-7b87af48cc96"/>
+    <ds:schemaRef ds:uri="dc163805-5a8a-4bac-b0c0-60a9bfcd087a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9054,12 +9056,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BAE7EAD-CAED-4699-A6FD-BC11EEB22633}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FB17129-D171-45DC-AA3C-DECEAA032B19}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e83e573-fb93-452c-9f3b-7b87af48cc96"/>
-    <ds:schemaRef ds:uri="dc163805-5a8a-4bac-b0c0-60a9bfcd087a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>